--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0003T0006Z000C1N40_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0003T0006Z000C1N40_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>2.6</v>
       </c>
       <c r="D2" t="n">
-        <v>14.5</v>
+        <v>2.35625</v>
       </c>
       <c r="E2" t="n">
-        <v>18.92958972735379</v>
+        <v>3.076058330694991</v>
       </c>
       <c r="F2" t="n">
-        <v>18.48752581099247</v>
+        <v>3.004222944286276</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.66069308044411</v>
+        <v>8.232362625572168</v>
       </c>
       <c r="D3" t="n">
-        <v>49.44973901240805</v>
+        <v>8.035582589516308</v>
       </c>
       <c r="E3" t="n">
-        <v>18.92958972735379</v>
+        <v>3.076058330694991</v>
       </c>
       <c r="F3" t="n">
-        <v>18.48752581099247</v>
+        <v>3.004222944286276</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>61.8418716134321</v>
+        <v>10.04930413718272</v>
       </c>
       <c r="D4" t="n">
-        <v>60.67991810797989</v>
+        <v>9.860486692546733</v>
       </c>
       <c r="E4" t="n">
-        <v>18.92958972735379</v>
+        <v>3.076058330694991</v>
       </c>
       <c r="F4" t="n">
-        <v>18.48752581099247</v>
+        <v>3.004222944286276</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>48.58096758868399</v>
+        <v>7.894407233161148</v>
       </c>
       <c r="D5" t="n">
-        <v>44.20719029585988</v>
+        <v>7.183668423077231</v>
       </c>
       <c r="E5" t="n">
-        <v>18.92958972735379</v>
+        <v>3.076058330694991</v>
       </c>
       <c r="F5" t="n">
-        <v>18.48752581099247</v>
+        <v>3.004222944286276</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>52.65307815026696</v>
+        <v>8.55612519941838</v>
       </c>
       <c r="D6" t="n">
-        <v>52.01443413022697</v>
+        <v>8.452345546161883</v>
       </c>
       <c r="E6" t="n">
-        <v>18.92958972735379</v>
+        <v>3.076058330694991</v>
       </c>
       <c r="F6" t="n">
-        <v>18.48752581099247</v>
+        <v>3.004222944286276</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.02335790692062</v>
+        <v>5.691295659874601</v>
       </c>
       <c r="D7" t="n">
-        <v>34.52709198513587</v>
+        <v>5.610652447584579</v>
       </c>
       <c r="E7" t="n">
-        <v>18.92958972735379</v>
+        <v>3.076058330694991</v>
       </c>
       <c r="F7" t="n">
-        <v>18.48752581099247</v>
+        <v>3.004222944286276</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>65.08916401614664</v>
+        <v>10.57698915262383</v>
       </c>
       <c r="D8" t="n">
-        <v>62.59610352292328</v>
+        <v>10.17186682247503</v>
       </c>
       <c r="E8" t="n">
-        <v>18.92958972735379</v>
+        <v>3.076058330694991</v>
       </c>
       <c r="F8" t="n">
-        <v>18.48752581099247</v>
+        <v>3.004222944286276</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.60216595131211</v>
+        <v>1.722851967088218</v>
       </c>
       <c r="D9" t="n">
-        <v>10.44693529310912</v>
+        <v>1.697626985130232</v>
       </c>
       <c r="E9" t="n">
-        <v>18.92958972735379</v>
+        <v>3.076058330694991</v>
       </c>
       <c r="F9" t="n">
-        <v>18.48752581099247</v>
+        <v>3.004222944286276</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
